--- a/Cenário em Ponte/Cromossomo NT/Resultados/Txt/Resultados Parametros/PSO/resultados_parametros_pop_4.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Resultados/Txt/Resultados Parametros/PSO/resultados_parametros_pop_4.xlsx
@@ -453,19 +453,19 @@
         <v>1.5</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.994714</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.9948129999999999</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.994714</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.9948129999999999</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.9948129999999999</v>
       </c>
     </row>
     <row r="3">
@@ -473,19 +473,19 @@
         <v>1.8</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.994714</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.9948129999999999</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.9958090000000001</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.9948129999999999</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.9948129999999999</v>
       </c>
     </row>
     <row r="4">
@@ -493,19 +493,19 @@
         <v>2.1</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.9963070000000001</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.99551</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.9948129999999999</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.9948129999999999</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.9948129999999999</v>
       </c>
     </row>
     <row r="5">
@@ -513,19 +513,19 @@
         <v>2.3</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.9963070000000001</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.9963070000000001</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.9963070000000001</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.9948129999999999</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.9963070000000001</v>
       </c>
     </row>
     <row r="6">
@@ -533,19 +533,19 @@
         <v>2.5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.9948129999999999</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.9948129999999999</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.996506</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.9948129999999999</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.985408</v>
+        <v>0.995012</v>
       </c>
     </row>
     <row r="7"/>

--- a/Cenário em Ponte/Cromossomo NT/Resultados/Txt/Resultados Parametros/PSO/resultados_parametros_pop_4.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Resultados/Txt/Resultados Parametros/PSO/resultados_parametros_pop_4.xlsx
@@ -428,127 +428,122 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C1" s="1" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="D1" s="1" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E1" s="1" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F1" s="1" t="n">
-        <v>2.5</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Combinação de Parâmetros</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Confiabilidade</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>1.5</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2.0, 2.0</t>
+        </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.994714</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>0.9948129999999999</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.994714</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0.9948129999999999</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0.9948129999999999</v>
+        <v>0.9905119999999999</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1.8</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1.5, 2.5</t>
+        </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0.994714</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>0.9948129999999999</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0.9958090000000001</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0.9948129999999999</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0.9948129999999999</v>
+        <v>0.993161</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2.1</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2.05, 1.9</t>
+        </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>0.9963070000000001</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>0.99551</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.9948129999999999</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0.9948129999999999</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.9948129999999999</v>
+        <v>0.991438</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>2.3</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2.2, 1.8</t>
+        </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.9963070000000001</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>0.9963070000000001</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0.9963070000000001</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0.9948129999999999</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.9963070000000001</v>
+        <v>0.991258</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>2.5</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1.8, 2.2</t>
+        </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0.9948129999999999</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>0.9948129999999999</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>0.996506</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>0.9948129999999999</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.995012</v>
-      </c>
-    </row>
-    <row r="7"/>
+        <v>0.992294</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2.1, 2.1</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0.9918169999999999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1.6, 2.4</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>0.992698</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2.3, 1.7</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>0.9906470000000001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1.9, 2.05</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>0.991044</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2.05, 2.05</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>0.99057</v>
+      </c>
+    </row>
+    <row r="12"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
